--- a/seed/2026年7月安全培训安排表.xlsx
+++ b/seed/2026年7月安全培训安排表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowHeight="20055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="51">
   <si>
     <t>日期</t>
   </si>
@@ -120,13 +120,22 @@
     <t>2026/7/13（周一）</t>
   </si>
   <si>
+    <t>危化品管理培训（第四场）</t>
+  </si>
+  <si>
     <t>2026/7/14（周二）</t>
   </si>
   <si>
+    <t>安全事故/事件调查技能专项培训  司索实操授权考试</t>
+  </si>
+  <si>
     <t>2026/7/15（周三）</t>
   </si>
   <si>
     <t>2026/7/16（周四）</t>
+  </si>
+  <si>
+    <t>动土作业安全管理专项培训</t>
   </si>
   <si>
     <t>2026/7/17（周五）</t>
@@ -1456,14 +1465,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I34"/>
-  <sheetFormatPr defaultColWidth="49.3090909090909" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="49.3083333333333" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22.9090909090909" style="1" customWidth="1"/>
-    <col min="2" max="3" width="36.5454545454545" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38.1818181818182" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.9083333333333" style="1" customWidth="1"/>
+    <col min="2" max="3" width="36.5416666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.1833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="57" style="1" customWidth="1"/>
-    <col min="6" max="6" width="49.2727272727273" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="49.3090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="49.275" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="49.3083333333333" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:9">
@@ -1681,11 +1690,13 @@
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="11" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>12</v>
@@ -1696,11 +1707,13 @@
       <c r="E16" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="11"/>
+      <c r="F16" s="11" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>8</v>
@@ -1715,7 +1728,7 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>12</v>
@@ -1726,11 +1739,13 @@
       <c r="E18" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="11" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>8</v>
@@ -1745,7 +1760,7 @@
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>17</v>
@@ -1760,7 +1775,7 @@
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B21" s="10"/>
       <c r="D21" s="10"/>
@@ -1769,7 +1784,7 @@
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>8</v>
@@ -1784,7 +1799,7 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>12</v>
@@ -1799,7 +1814,7 @@
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>8</v>
@@ -1814,7 +1829,7 @@
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>12</v>
@@ -1829,7 +1844,7 @@
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>8</v>
@@ -1844,7 +1859,7 @@
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>17</v>
@@ -1859,7 +1874,7 @@
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B28" s="10"/>
       <c r="D28" s="10"/>
@@ -1868,7 +1883,7 @@
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>8</v>
@@ -1883,7 +1898,7 @@
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>12</v>
@@ -1898,7 +1913,7 @@
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>8</v>
@@ -1913,7 +1928,7 @@
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>12</v>
@@ -1928,7 +1943,7 @@
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>8</v>
@@ -1943,7 +1958,7 @@
     </row>
     <row r="34" ht="30" customHeight="1" spans="1:6">
       <c r="A34" s="14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1964,7 +1979,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
